--- a/功能模块.xlsx
+++ b/功能模块.xlsx
@@ -1,52 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -64,14 +44,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,94 +447,372 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>模块</v>
-      </c>
-      <c r="B1" t="str">
-        <v>需求列表</v>
-      </c>
-      <c r="C1" t="str">
-        <v>预估工时</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>需求列表</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>预估工时</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>学生管理</v>
-      </c>
-      <c r="B2" t="str">
-        <v>学生 CRUD + 基本信息</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1 周</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>学生 CRUD + 基本信息 + 多学科课程卡片</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1 周</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>个性化学习计划</v>
-      </c>
-      <c r="B3" t="str">
-        <v>知识点拆解 + 状态管理</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2 周</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>学生分组管理（班级/小组双维度 + 左侧分组树 + 卡片标签 + 筛选器）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>课堂记录</v>
-      </c>
-      <c r="B4" t="str">
-        <v>新增/查看/编辑记录</v>
-      </c>
-      <c r="C4" t="str">
-        <v>1 周</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>班级管理（增删改查 + 成员管理）</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>资料库</v>
-      </c>
-      <c r="B5" t="str">
-        <v>上传/存储/分类/标签</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2 周</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小组管理（增删改查 + 成员管理）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>资料分配</v>
-      </c>
-      <c r="B6" t="str">
-        <v>单学生分配 + 多学生分配</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2 周</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>分组内成员增删 + 跨组移动学生</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>**总计（MVP）**</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v>**6 周（2 个迭代）**</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>学生管理</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>学生错题本入口（卡片显眼入口 + 按科目错题概览）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>个性化学习计划</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>知识点拆解 + 状态管理</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>新增/查看/编辑记录</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>资料库</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>上传/存储/分类/标签</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>资料库</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>给班级/小组批量分配资料</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>资料分配</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>单学生分配 + 多学生分配</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2 周</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>课程表</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>按班级颜色/标签区分课程</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>课程表</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>按班级查看排课视图切换</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>课堂记录/报告</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>按班级/小组维度聚合查看</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>仪表盘/工作台</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>按班级切换维度查看整体概况</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>外部共享资料连接</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FTP/SMB 等共享协议连接</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>macOS 优先支持</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>教师端优先适配 macOS 桌面环境</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>移动端支持</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>移动端核心功能查看与轻量操作</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>系统提醒调用</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>课程、作业、批改、报告等关键事项提醒</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>待估</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>**总计（MVP）**</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>**6 周（2 个迭代）**</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>